--- a/src/Tests.Skia/ExcelColumnMetadataTests.ColumnMetadataMissingPartIsBenign.verified.xlsx
+++ b/src/Tests.Skia/ExcelColumnMetadataTests.ColumnMetadataMissingPartIsBenign.verified.xlsx
@@ -28,5 +28,6 @@
       </c>
     </row>
   </sheetData>
+  <pageSetup paperSize="9"/>
 </worksheet>
 </file>
--- a/src/Tests.Skia/ExcelColumnMetadataTests.ColumnMetadataMissingPartIsBenign.verified.xlsx
+++ b/src/Tests.Skia/ExcelColumnMetadataTests.ColumnMetadataMissingPartIsBenign.verified.xlsx
@@ -28,6 +28,5 @@
       </c>
     </row>
   </sheetData>
-  <pageSetup paperSize="9"/>
 </worksheet>
 </file>